--- a/docs/Mileage-Master-Sitemap.xlsx
+++ b/docs/Mileage-Master-Sitemap.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Navigation" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Sitemap!$A$1:$K$31</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Sitemap!$A$1:$L$33</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="287">
   <si>
     <t xml:space="preserve">Mileage Master — Website Sitemap</t>
   </si>
@@ -63,6 +63,24 @@
     <t xml:space="preserve">905.602.6897 · orders@oemfleets.ca · Mon–Fri 8:00–5:00 EST</t>
   </si>
   <si>
+    <t xml:space="preserve">POSITIONING STATEMENTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retail clients (drivers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality you can trust. Value we can deliver.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garages (shops &amp; installers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your customer trusts you. You can trust us.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Positioning statement column on the Sitemap tab shows where each line is used.</t>
+  </si>
+  <si>
     <t xml:space="preserve">AT A GLANCE</t>
   </si>
   <si>
@@ -114,6 +132,12 @@
     <t xml:space="preserve">Built from the Domain cell above (C7). Change the domain there and every URL updates.</t>
   </si>
   <si>
+    <t xml:space="preserve">Positioning statement column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which positioning line a page or section uses: Retail, Garage or both. For Proposed pages it is a suggestion.</t>
+  </si>
+  <si>
     <t xml:space="preserve">#anchor links</t>
   </si>
   <si>
@@ -129,7 +153,7 @@
     <t xml:space="preserve">├── Home  /</t>
   </si>
   <si>
-    <t xml:space="preserve">│   ├── Hero — Quality you can trust. Value we can deliver.</t>
+    <t xml:space="preserve">│   ├── Hero — Quality you can trust. Value we can deliver.  [Retail]</t>
   </si>
   <si>
     <t xml:space="preserve">│   ├── Find the right oil  (#finder)</t>
@@ -147,7 +171,7 @@
     <t xml:space="preserve">│   ├── What shops say (testimonials)</t>
   </si>
   <si>
-    <t xml:space="preserve">│   ├── Become a dealer / wholesale pricing  (#dealers, #quote)</t>
+    <t xml:space="preserve">│   ├── Become a dealer — Your customer trusts you. You can trust us.  [Garage]</t>
   </si>
   <si>
     <t xml:space="preserve">│   └── Order today contact bar</t>
@@ -162,7 +186,7 @@
     <t xml:space="preserve">│   ├── Product recommendations — results  (#results)</t>
   </si>
   <si>
-    <t xml:space="preserve">│   ├── Case pricing  (#pricing)</t>
+    <t xml:space="preserve">│   ├── Case pricing — Your customer trusts you. You can trust us.  [Garage]</t>
   </si>
   <si>
     <t xml:space="preserve">│   └── Vehicle not listed?  (#help)</t>
@@ -171,6 +195,9 @@
     <t xml:space="preserve">├── Sitemap  /sitemap/</t>
   </si>
   <si>
+    <t xml:space="preserve">│   └── Wholesale pricing — Your customer trusts you. You can trust us.  [Garage]</t>
+  </si>
+  <si>
     <t xml:space="preserve">└── Proposed: Products · Spec &amp; safety data sheets · Warranty · About · Contact · Privacy · Terms</t>
   </si>
   <si>
@@ -198,6 +225,9 @@
     <t xml:space="preserve">Main call to action</t>
   </si>
   <si>
+    <t xml:space="preserve">Positioning statement</t>
+  </si>
+  <si>
     <t xml:space="preserve">Audience</t>
   </si>
   <si>
@@ -225,13 +255,16 @@
     <t xml:space="preserve">Find my oil · Get wholesale pricing</t>
   </si>
   <si>
+    <t xml:space="preserve">Retail + Garage</t>
+  </si>
+  <si>
     <t xml:space="preserve">Drivers &amp; shops</t>
   </si>
   <si>
     <t xml:space="preserve">Live</t>
   </si>
   <si>
-    <t xml:space="preserve">SEO priority 1.0 — updated monthly.</t>
+    <t xml:space="preserve">SEO priority 1.0 — updated monthly. Retail line is also the browser tab title, Google description and brand slogan.</t>
   </si>
   <si>
     <t xml:space="preserve">1.1</t>
@@ -249,7 +282,7 @@
     <t xml:space="preserve">FIND MY OIL · GET WHOLESALE PRICING</t>
   </si>
   <si>
-    <t xml:space="preserve">Product photo is a mockup — replace with real photography before launch.</t>
+    <t xml:space="preserve">Retail line is the main headline; Garage line closes the intro paragraph. Product photo is a mockup — replace with real photography before launch.</t>
   </si>
   <si>
     <t xml:space="preserve">1.2</t>
@@ -354,10 +387,13 @@
     <t xml:space="preserve">Request wholesale pricing (form)</t>
   </si>
   <si>
+    <t xml:space="preserve">Garage</t>
+  </si>
+  <si>
     <t xml:space="preserve">Shops, jobbers, installers</t>
   </si>
   <si>
-    <t xml:space="preserve">Form fields: business name, phone, email, details.</t>
+    <t xml:space="preserve">Heading: Your customer trusts you. You can trust us. Form fields: business name, phone, email, details.</t>
   </si>
   <si>
     <t xml:space="preserve">1.8</t>
@@ -465,6 +501,9 @@
     <t xml:space="preserve">Priced by the case; quotes same business day. Quote request form.</t>
   </si>
   <si>
+    <t xml:space="preserve">Heading: Your customer trusts you. You can trust us.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.4</t>
   </si>
   <si>
@@ -498,6 +537,21 @@
     <t xml:space="preserve">SEO priority 0.3.</t>
   </si>
   <si>
+    <t xml:space="preserve">3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wholesale pricing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/sitemap/#pricing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priced by the case; quote request form.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">4</t>
   </si>
   <si>
@@ -534,6 +588,9 @@
     <t xml:space="preserve">Find my oil · Request pricing</t>
   </si>
   <si>
+    <t xml:space="preserve">Retail</t>
+  </si>
+  <si>
     <t xml:space="preserve">Proposed</t>
   </si>
   <si>
@@ -762,6 +819,15 @@
     <t xml:space="preserve">Home › Become a dealer</t>
   </si>
   <si>
+    <t xml:space="preserve">Footer — Brand block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logo + Quality you can trust. Value we can deliver. + address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retail positioning sign-off (Home and Sitemap pages; the Oil Finder has a compact footer without it)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Footer — Products</t>
   </si>
   <si>
@@ -781,9 +847,6 @@
   </si>
   <si>
     <t xml:space="preserve">Footer — For shops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wholesale pricing</t>
   </si>
   <si>
     <t xml:space="preserve">/#quote</t>
@@ -833,7 +896,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -896,6 +959,22 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFC8102E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFC8102E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF555555"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -998,7 +1077,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1027,6 +1106,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1039,11 +1126,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1059,7 +1146,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1075,7 +1162,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1083,11 +1170,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1448,7 +1535,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C43"/>
+  <dimension ref="B2:C50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -1512,191 +1599,230 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="7" t="n">
-        <f aca="false">COUNTIFS(Sitemap!$D:$D,"Page",Sitemap!$J:$J,"Live")</f>
+      <c r="C12" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <f aca="false">COUNTIFS(Sitemap!$D:$D,"Page",Sitemap!$K:$K,"Live")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <f aca="false">COUNTIFS(Sitemap!$D:$D,"Section",Sitemap!$K:$K,"Live")</f>
         <v>14</v>
       </c>
-      <c r="C13" s="7" t="n">
-        <f aca="false">COUNTIFS(Sitemap!$D:$D,"Section",Sitemap!$J:$J,"Live")</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <f aca="false">COUNTIFS(Sitemap!$D:$D,"Page",Sitemap!$J:$J,"Proposed")</f>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <f aca="false">COUNTIFS(Sitemap!$D:$D,"Page",Sitemap!$K:$K,"Proposed")</f>
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="7" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="9" t="n">
         <f aca="false">COUNTIF(Navigation!$A:$A,"Header menu")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="7" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="9" t="n">
         <f aca="false">COUNTIF(Navigation!$A:$A,"Footer*")</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="8" t="s">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C24" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="8" t="s">
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C25" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="8" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C26" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="6" t="s">
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10" t="s">
+      <c r="C27" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="10" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C28" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>35</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="10" t="s">
-        <v>37</v>
+      <c r="B32" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="10" t="s">
-        <v>38</v>
+      <c r="B33" s="12" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="10" t="s">
-        <v>39</v>
+      <c r="B34" s="12" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="10" t="s">
-        <v>40</v>
+      <c r="B35" s="12" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="10" t="s">
-        <v>41</v>
+      <c r="B36" s="12" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="10" t="s">
-        <v>42</v>
+      <c r="B37" s="12" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="10" t="s">
-        <v>43</v>
+      <c r="B38" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="10" t="s">
-        <v>44</v>
+      <c r="B39" s="12" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="10" t="s">
-        <v>45</v>
+      <c r="B40" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="10" t="s">
-        <v>46</v>
+      <c r="B41" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="10" t="s">
-        <v>47</v>
+      <c r="B42" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="10" t="s">
-        <v>48</v>
+      <c r="B43" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="12" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1715,7 +1841,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="2" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="7"/>
@@ -1725,1082 +1851,1215 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="60"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="J1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="13" t="n">
+      <c r="D1" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" s="15" t="str">
+      <c r="C2" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="17" t="str">
         <f aca="false">Overview!$C$7&amp;E2</f>
         <v>https://mileagemaster.ca/</v>
       </c>
-      <c r="G2" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>68</v>
+      <c r="G2" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A3" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="17" t="n">
+      <c r="A3" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="19" t="str">
+      <c r="C3" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E3</f>
         <v>https://mileagemaster.ca/</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K3" s="16" t="s">
-        <v>74</v>
+      <c r="G3" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="17" t="n">
+      <c r="A4" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="19" t="str">
+      <c r="C4" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E4</f>
         <v>https://mileagemaster.ca/#finder</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="J4" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K4" s="16"/>
+      <c r="L4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="17" t="n">
+      <c r="A5" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" s="16" t="s">
+      <c r="C5" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="19" t="str">
+      <c r="E5" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E5</f>
         <v>https://mileagemaster.ca/#grades</v>
       </c>
-      <c r="G5" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K5" s="16"/>
+      <c r="G5" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="17" t="n">
+      <c r="A6" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="F6" s="19" t="str">
+      <c r="C6" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E6</f>
         <v>https://mileagemaster.ca/#grades</v>
       </c>
-      <c r="G6" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K6" s="16"/>
+      <c r="G6" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A7" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="17" t="n">
+      <c r="A7" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="F7" s="19" t="str">
+      <c r="C7" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E7</f>
         <v>https://mileagemaster.ca/#europe</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K7" s="16"/>
+      <c r="G7" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="17" t="n">
+      <c r="A8" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" s="19" t="str">
+      <c r="C8" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E8</f>
         <v>https://mileagemaster.ca/#specs</v>
       </c>
-      <c r="G8" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>99</v>
+      <c r="G8" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="18" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A9" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B9" s="17" t="n">
+      <c r="A9" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="19" t="str">
+      <c r="C9" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E9</f>
         <v>https://mileagemaster.ca/</v>
       </c>
-      <c r="G9" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="J9" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>103</v>
+      <c r="G9" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L9" s="18" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10" s="17" t="n">
+      <c r="A10" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="F10" s="19" t="str">
+      <c r="C10" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E10</f>
         <v>https://mileagemaster.ca/#dealers</v>
       </c>
-      <c r="G10" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="J10" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>110</v>
+      <c r="G10" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A11" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B11" s="17" t="n">
+      <c r="A11" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="19" t="str">
+      <c r="C11" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E11</f>
         <v>https://mileagemaster.ca/</v>
       </c>
-      <c r="G11" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K11" s="16"/>
+      <c r="G11" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L11" s="18"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" s="13" t="n">
+      <c r="A12" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="F12" s="15" t="str">
+      <c r="C12" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12" s="17" t="str">
         <f aca="false">Overview!$C$7&amp;E12</f>
         <v>https://mileagemaster.ca/oil-finder/</v>
       </c>
-      <c r="G12" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>120</v>
+      <c r="G12" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A13" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="B13" s="17" t="n">
+      <c r="A13" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="19" t="str">
+      <c r="C13" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E13</f>
         <v>https://mileagemaster.ca/oil-finder/#finder</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>126</v>
+      <c r="G13" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L13" s="18" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A14" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="B14" s="17" t="n">
+      <c r="A14" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="F14" s="19" t="str">
+      <c r="C14" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F14" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E14</f>
         <v>https://mileagemaster.ca/oil-finder/#results</v>
       </c>
-      <c r="G14" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="I14" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K14" s="16" t="s">
-        <v>132</v>
+      <c r="G14" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L14" s="18" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A15" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="B15" s="17" t="n">
+      <c r="A15" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="F15" s="19" t="str">
+      <c r="C15" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F15" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E15</f>
         <v>https://mileagemaster.ca/oil-finder/#results</v>
       </c>
-      <c r="G15" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K15" s="16"/>
+      <c r="G15" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A16" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" s="17" t="n">
+      <c r="A16" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="F16" s="19" t="str">
+      <c r="C16" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E16</f>
         <v>https://mileagemaster.ca/oil-finder/#results</v>
       </c>
-      <c r="G16" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K16" s="16"/>
+      <c r="G16" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L16" s="18"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A17" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B17" s="17" t="n">
+      <c r="A17" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="F17" s="19" t="str">
+      <c r="C17" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F17" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E17</f>
         <v>https://mileagemaster.ca/oil-finder/#results</v>
       </c>
-      <c r="G17" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K17" s="16"/>
+      <c r="G17" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L17" s="18"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A18" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="B18" s="17" t="n">
+      <c r="A18" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="B18" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="F18" s="19" t="str">
+      <c r="C18" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="F18" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E18</f>
         <v>https://mileagemaster.ca/oil-finder/#pricing</v>
       </c>
-      <c r="G18" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="I18" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="J18" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K18" s="16"/>
+      <c r="G18" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A19" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="B19" s="17" t="n">
+      <c r="A19" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="F19" s="19" t="str">
+      <c r="C19" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F19" s="21" t="str">
         <f aca="false">Overview!$C$7&amp;E19</f>
         <v>https://mileagemaster.ca/oil-finder/#help</v>
       </c>
-      <c r="G19" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>150</v>
+      <c r="G19" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L19" s="18" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="B20" s="13" t="n">
+      <c r="A20" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="B20" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="F20" s="15" t="str">
+      <c r="C20" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="F20" s="17" t="str">
         <f aca="false">Overview!$C$7&amp;E20</f>
         <v>https://mileagemaster.ca/sitemap/</v>
       </c>
-      <c r="G20" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="K20" s="12" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B21" s="13" t="n">
+      <c r="G20" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="F21" s="21" t="str">
+        <f aca="false">Overview!$C$7&amp;E21</f>
+        <v>https://mileagemaster.ca/sitemap/#pricing</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="F22" s="21" t="str">
+        <f aca="false">Overview!$C$7&amp;E22</f>
+        <v>https://mileagemaster.ca/sitemap/</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L22" s="18"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="F21" s="15" t="str">
-        <f aca="false">Overview!$C$7&amp;E21</f>
+      <c r="C23" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="F23" s="17" t="str">
+        <f aca="false">Overview!$C$7&amp;E23</f>
         <v>https://mileagemaster.ca/sitemap.xml</v>
       </c>
-      <c r="G21" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="K21" s="12" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="B22" s="13" t="n">
+      <c r="G23" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B24" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F22" s="15" t="str">
-        <f aca="false">Overview!$C$7&amp;E22</f>
+      <c r="C24" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F24" s="17" t="str">
+        <f aca="false">Overview!$C$7&amp;E24</f>
         <v>https://mileagemaster.ca/products/</v>
       </c>
-      <c r="G22" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="H22" s="12" t="s">
+      <c r="G24" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A25" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="F25" s="21" t="str">
+        <f aca="false">Overview!$C$7&amp;E25</f>
+        <v>https://mileagemaster.ca/products/premium-full-synthetic/</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="L25" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A26" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="F26" s="21" t="str">
+        <f aca="false">Overview!$C$7&amp;E26</f>
+        <v>https://mileagemaster.ca/products/high-mileage/</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="I26" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="J26" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="L26" s="18"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A27" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="F27" s="21" t="str">
+        <f aca="false">Overview!$C$7&amp;E27</f>
+        <v>https://mileagemaster.ca/products/synthetic-blend/</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="I27" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="L27" s="18"/>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="F28" s="17" t="str">
+        <f aca="false">Overview!$C$7&amp;E28</f>
+        <v>https://mileagemaster.ca/documents/</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="F29" s="17" t="str">
+        <f aca="false">Overview!$C$7&amp;E29</f>
+        <v>https://mileagemaster.ca/warranty/</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="L29" s="14" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="F30" s="17" t="str">
+        <f aca="false">Overview!$C$7&amp;E30</f>
+        <v>https://mileagemaster.ca/about/</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="J30" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="I22" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A23" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="B23" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="F23" s="19" t="str">
-        <f aca="false">Overview!$C$7&amp;E23</f>
-        <v>https://mileagemaster.ca/products/premium-full-synthetic/</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="I23" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="J23" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="K23" s="16"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A24" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="B24" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="F24" s="19" t="str">
-        <f aca="false">Overview!$C$7&amp;E24</f>
-        <v>https://mileagemaster.ca/products/high-mileage/</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="I24" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="J24" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="K24" s="16"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A25" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B25" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="F25" s="19" t="str">
-        <f aca="false">Overview!$C$7&amp;E25</f>
-        <v>https://mileagemaster.ca/products/synthetic-blend/</v>
-      </c>
-      <c r="G25" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="I25" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="J25" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="K25" s="16"/>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="B26" s="13" t="n">
+      <c r="K30" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="L30" s="14"/>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B31" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="F26" s="15" t="str">
-        <f aca="false">Overview!$C$7&amp;E26</f>
-        <v>https://mileagemaster.ca/documents/</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="H26" s="12" t="s">
+      <c r="C31" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F31" s="17" t="str">
+        <f aca="false">Overview!$C$7&amp;E31</f>
+        <v>https://mileagemaster.ca/contact/</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="K31" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="I26" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="K26" s="12" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="B27" s="13" t="n">
+      <c r="L31" s="14" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="B32" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="F27" s="15" t="str">
-        <f aca="false">Overview!$C$7&amp;E27</f>
-        <v>https://mileagemaster.ca/warranty/</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="J27" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="K27" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B28" s="13" t="n">
+      <c r="C32" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F32" s="17" t="str">
+        <f aca="false">Overview!$C$7&amp;E32</f>
+        <v>https://mileagemaster.ca/privacy/</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B33" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="F28" s="15" t="str">
-        <f aca="false">Overview!$C$7&amp;E28</f>
-        <v>https://mileagemaster.ca/about/</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="J28" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="K28" s="12"/>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="B29" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="F29" s="15" t="str">
-        <f aca="false">Overview!$C$7&amp;E29</f>
-        <v>https://mileagemaster.ca/contact/</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="J29" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="K29" s="12" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="B30" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="F30" s="15" t="str">
-        <f aca="false">Overview!$C$7&amp;E30</f>
-        <v>https://mileagemaster.ca/privacy/</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="K30" s="12" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="B31" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="F31" s="15" t="str">
-        <f aca="false">Overview!$C$7&amp;E31</f>
+      <c r="C33" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="F33" s="17" t="str">
+        <f aca="false">Overview!$C$7&amp;E33</f>
         <v>https://mileagemaster.ca/terms/</v>
       </c>
-      <c r="G31" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="K31" s="12"/>
+      <c r="G33" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="L33" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K31"/>
-  <conditionalFormatting sqref="J2:J31">
+  <autoFilter ref="A1:L33"/>
+  <conditionalFormatting sqref="K2:K33">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
-      <formula>$J2="Live"</formula>
+      <formula>$K2="Live"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
-      <formula>$J2="Proposed"</formula>
+      <formula>$K2="Proposed"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J31" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K33" type="list">
       <formula1>"Live,Proposed,Approved,Removed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2821,7 +3080,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -2832,389 +3091,406 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="D1" s="21" t="s">
+      <c r="A1" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="E1" s="21" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+      <c r="D18" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="E21" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="B2" s="17" t="n">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="B22" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="B3" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="B4" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="B5" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="B6" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="B7" s="17" t="n">
+      <c r="C22" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="B23" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="B8" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="B9" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="B10" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" s="16" t="s">
+      <c r="C23" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="B11" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="16" t="s">
+      <c r="E23" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="B12" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="B13" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="B14" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="B15" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="B16" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="B17" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="B18" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="B19" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="B20" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="B21" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="B22" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
